--- a/data/trans_dic/IP19C02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por limpieza de boca</t>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 23,63</t>
+          <t>7,03; 23,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,67</t>
+          <t>1,24; 12,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 44,1</t>
+          <t>13,88; 43,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,54; 59,82</t>
+          <t>22,88; 61,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,78</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,76</t>
+          <t>0,0; 10,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,32; 54,26</t>
+          <t>23,25; 52,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,47; 64,58</t>
+          <t>27,4; 65,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 14,66</t>
+          <t>4,45; 13,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,11</t>
+          <t>1,43; 8,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,53; 44,44</t>
+          <t>22,76; 45,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,27; 56,82</t>
+          <t>29,66; 57,96</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,34</t>
+          <t>4,45; 9,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,02</t>
+          <t>3,68; 9,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,15; 23,35</t>
+          <t>15,06; 22,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,82; 34,91</t>
+          <t>25,59; 35,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,09</t>
+          <t>4,19; 9,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,29</t>
+          <t>3,81; 9,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,9; 24,69</t>
+          <t>15,93; 24,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,51; 38,98</t>
+          <t>28,05; 39,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,67</t>
+          <t>4,73; 8,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,17</t>
+          <t>4,42; 8,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 22,36</t>
+          <t>16,62; 22,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,15; 35,55</t>
+          <t>27,96; 35,58</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 12,23</t>
+          <t>2,57; 11,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 11,0</t>
+          <t>2,49; 11,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,52; 25,46</t>
+          <t>11,29; 24,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,94; 32,68</t>
+          <t>18,65; 32,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 16,11</t>
+          <t>4,68; 16,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 16,0</t>
+          <t>4,71; 16,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 19,04</t>
+          <t>6,89; 18,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 32,07</t>
+          <t>17,75; 31,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 11,33</t>
+          <t>4,29; 11,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 11,74</t>
+          <t>4,47; 11,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 19,71</t>
+          <t>10,76; 19,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,24; 29,9</t>
+          <t>19,93; 29,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,96</t>
+          <t>5,2; 9,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,09</t>
+          <t>3,9; 8,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 22,53</t>
+          <t>15,74; 22,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,58; 33,85</t>
+          <t>25,63; 34,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,18</t>
+          <t>4,89; 9,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,85</t>
+          <t>4,61; 8,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,92; 23,03</t>
+          <t>16,14; 23,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,22; 35,7</t>
+          <t>27,38; 35,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,89</t>
+          <t>5,53; 8,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,74</t>
+          <t>4,76; 7,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 21,65</t>
+          <t>16,97; 21,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,74; 33,94</t>
+          <t>27,7; 33,7</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6553</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5857</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11731</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10618</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>11666</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7907</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16474</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>23398</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3300; 10998</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>596; 5799</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3074; 9685</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6803; 18368</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4113</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4589</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6544; 14711</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6983; 16637</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3995; 12569</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1302; 8089</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11444; 22641</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>16377; 32002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>14827</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13367</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47545</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79289</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16007</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14494</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>50737</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>107227</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>30834</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>27861</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>98281</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>186516</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10156; 21567</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8080; 20376</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38074; 57841</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67006; 92520</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10301; 22813</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9188; 21814</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>40178; 62511</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>90593; 126108</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>22445; 39533</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>20364; 37551</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>83934; 112562</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>163547; 208089</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4361</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5043</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15377</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25319</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7244</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10584</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>33617</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11141</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12286</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25961</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>58936</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1942; 8968</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2127; 10143</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9904; 21718</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18663; 32935</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3424; 11717</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3872; 13276</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6046; 16657</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>24133; 42699</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6387; 17274</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7488; 19073</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18877; 34784</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>47042; 70104</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>25741</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20361</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>68778</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116339</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>152510</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>49882</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>43572</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>140716</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>268849</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>18261; 33783</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13779; 28946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>57080; 82128</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>100387; 133507</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17678; 32695</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16876; 32379</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>59392; 85650</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>132619; 173719</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>39392; 61615</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>34252; 56189</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>123958; 159082</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>242682; 295243</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 23,44</t>
+          <t>7,2; 23,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,09</t>
+          <t>1,23; 11,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,88; 43,75</t>
+          <t>14,04; 44,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,88; 61,78</t>
+          <t>19,51; 59,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,59</t>
+          <t>0,0; 9,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,68</t>
+          <t>0,0; 12,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,25; 52,27</t>
+          <t>24,26; 54,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,4; 65,28</t>
+          <t>29,53; 64,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 13,99</t>
+          <t>5,12; 15,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,9</t>
+          <t>1,47; 8,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,76; 45,03</t>
+          <t>22,37; 44,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,66; 57,96</t>
+          <t>28,71; 56,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,45</t>
+          <t>4,28; 9,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,27</t>
+          <t>4,06; 9,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,06; 22,89</t>
+          <t>14,99; 23,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,59; 35,34</t>
+          <t>25,15; 34,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,28</t>
+          <t>4,19; 9,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,05</t>
+          <t>3,99; 9,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 24,79</t>
+          <t>16,01; 24,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,05; 39,04</t>
+          <t>27,64; 38,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,34</t>
+          <t>4,86; 8,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,15</t>
+          <t>4,31; 8,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,62; 22,29</t>
+          <t>16,61; 22,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,96; 35,58</t>
+          <t>28,2; 35,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,85</t>
+          <t>1,97; 11,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 11,86</t>
+          <t>2,5; 11,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 24,75</t>
+          <t>10,92; 25,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 32,91</t>
+          <t>18,82; 32,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 16,02</t>
+          <t>4,8; 16,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 16,17</t>
+          <t>4,13; 15,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 18,99</t>
+          <t>7,2; 18,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,75; 31,41</t>
+          <t>18,97; 31,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,61</t>
+          <t>4,66; 12,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,38</t>
+          <t>4,48; 11,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,76; 19,83</t>
+          <t>10,64; 19,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,93; 29,7</t>
+          <t>20,14; 29,93</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,63</t>
+          <t>5,27; 9,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,19</t>
+          <t>3,92; 7,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 22,65</t>
+          <t>15,68; 22,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 34,09</t>
+          <t>25,56; 33,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,04</t>
+          <t>4,79; 9,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,85</t>
+          <t>4,56; 8,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,14; 23,27</t>
+          <t>16,33; 23,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,38; 35,86</t>
+          <t>27,2; 35,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,65</t>
+          <t>5,59; 8,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,81</t>
+          <t>4,8; 7,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,77</t>
+          <t>17,07; 21,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,7; 33,7</t>
+          <t>27,75; 33,78</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3300; 10998</t>
+          <t>3378; 11250</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>596; 5799</t>
+          <t>592; 5423</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3074; 9685</t>
+          <t>3107; 9753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6803; 18368</t>
+          <t>5802; 17815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 4127</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4589</t>
+          <t>0; 5217</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6544; 14711</t>
+          <t>6826; 15216</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6983; 16637</t>
+          <t>7526; 16325</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3995; 12569</t>
+          <t>4598; 13791</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1302; 8089</t>
+          <t>1336; 8013</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11444; 22641</t>
+          <t>11248; 22246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16377; 32002</t>
+          <t>15853; 31333</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10156; 21567</t>
+          <t>9769; 21490</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8080; 20376</t>
+          <t>8921; 19957</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38074; 57841</t>
+          <t>37895; 58575</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67006; 92520</t>
+          <t>65861; 90907</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10301; 22813</t>
+          <t>10302; 23225</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9188; 21814</t>
+          <t>9616; 22793</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40178; 62511</t>
+          <t>40364; 62076</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90593; 126108</t>
+          <t>89272; 123846</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22445; 39533</t>
+          <t>23017; 40845</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20364; 37551</t>
+          <t>19866; 37306</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83934; 112562</t>
+          <t>83887; 113648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>163547; 208089</t>
+          <t>164930; 210477</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1942; 8968</t>
+          <t>1489; 8380</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2127; 10143</t>
+          <t>2136; 9691</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9904; 21718</t>
+          <t>9581; 21933</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18663; 32935</t>
+          <t>18837; 32649</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3424; 11717</t>
+          <t>3508; 12117</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3872; 13276</t>
+          <t>3394; 13077</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6046; 16657</t>
+          <t>6318; 16269</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24133; 42699</t>
+          <t>25791; 43414</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6387; 17274</t>
+          <t>6931; 18093</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7488; 19073</t>
+          <t>7518; 18830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18877; 34784</t>
+          <t>18669; 34180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47042; 70104</t>
+          <t>47537; 70644</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18261; 33783</t>
+          <t>18506; 34662</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13779; 28946</t>
+          <t>13830; 27968</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57080; 82128</t>
+          <t>56846; 81368</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100387; 133507</t>
+          <t>100101; 131230</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17678; 32695</t>
+          <t>17312; 32665</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16876; 32379</t>
+          <t>16690; 31697</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59392; 85650</t>
+          <t>60081; 86057</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>132619; 173719</t>
+          <t>131763; 173549</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39392; 61615</t>
+          <t>39819; 60805</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34252; 56189</t>
+          <t>34508; 53864</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123958; 159082</t>
+          <t>124700; 158533</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>242682; 295243</t>
+          <t>243120; 295973</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49,19%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,96%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,07%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>26,45%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,73%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 23,97</t>
+          <t>0,0; 9,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,31</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,04; 44,05</t>
+          <t>24,32; 54,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,51; 59,92</t>
+          <t>30,91; 68,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,62</t>
+          <t>7,23; 23,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,14</t>
+          <t>1,23; 10,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,26; 54,07</t>
+          <t>13,08; 44,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,53; 64,06</t>
+          <t>26,18; 60,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 15,35</t>
+          <t>4,94; 14,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,81</t>
+          <t>1,43; 9,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,37; 44,24</t>
+          <t>22,53; 44,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,71; 56,75</t>
+          <t>32,46; 58,69</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35,13%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,49%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>18,81%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,12%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,41</t>
+          <t>4,06; 9,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,08</t>
+          <t>3,85; 9,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,99; 23,18</t>
+          <t>15,9; 24,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,15; 34,72</t>
+          <t>29,41; 41,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,45</t>
+          <t>4,18; 9,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,46</t>
+          <t>3,61; 9,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 24,62</t>
+          <t>15,15; 23,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,64; 38,34</t>
+          <t>26,74; 37,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,62</t>
+          <t>4,85; 8,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,1</t>
+          <t>4,44; 8,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 22,51</t>
+          <t>16,74; 22,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,2; 35,99</t>
+          <t>29,99; 37,59</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,89%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>17,53%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,07</t>
+          <t>4,67; 16,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 11,33</t>
+          <t>4,83; 16,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,92; 25,0</t>
+          <t>7,08; 19,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 32,62</t>
+          <t>20,38; 34,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 16,57</t>
+          <t>2,44; 12,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 15,92</t>
+          <t>2,43; 11,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 18,55</t>
+          <t>11,52; 25,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,97; 31,93</t>
+          <t>19,52; 33,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 12,16</t>
+          <t>4,26; 11,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 11,23</t>
+          <t>4,54; 11,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 19,48</t>
+          <t>10,63; 19,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,14; 29,93</t>
+          <t>21,57; 31,68</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,88</t>
+          <t>4,79; 9,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,92</t>
+          <t>4,56; 8,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,68; 22,44</t>
+          <t>15,92; 23,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,56; 33,51</t>
+          <t>29,28; 37,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,03</t>
+          <t>5,47; 9,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,66</t>
+          <t>4,02; 8,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,38</t>
+          <t>15,77; 22,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,2; 35,82</t>
+          <t>26,78; 35,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,53</t>
+          <t>5,61; 8,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,49</t>
+          <t>4,69; 7,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 21,7</t>
+          <t>16,83; 21,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,75; 33,78</t>
+          <t>29,68; 35,79</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10618</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11947</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>6553</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1951</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5857</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11731</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1474</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10618</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23398</t>
+          <t>23093</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3378; 11250</t>
+          <t>0; 4193</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>592; 5423</t>
+          <t>0; 5051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3107; 9753</t>
+          <t>6845; 15269</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5802; 17815</t>
+          <t>7509; 16531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4127</t>
+          <t>3391; 11089</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5217</t>
+          <t>590; 5117</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6826; 15216</t>
+          <t>2897; 9764</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7526; 16325</t>
+          <t>6974; 16171</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4598; 13791</t>
+          <t>4436; 13166</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1336; 8013</t>
+          <t>1298; 8287</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11248; 22246</t>
+          <t>11330; 22344</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15853; 31333</t>
+          <t>16535; 29891</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>112</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16007</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14494</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50737</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108741</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>14827</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13367</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>47545</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79289</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16007</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14494</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50737</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>107227</t>
+          <t>86200</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>186516</t>
+          <t>194941</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9769; 21490</t>
+          <t>9973; 22333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8921; 19957</t>
+          <t>9278; 22390</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37895; 58575</t>
+          <t>40102; 62249</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65861; 90907</t>
+          <t>91046; 127120</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10302; 23225</t>
+          <t>9536; 21321</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9616; 22793</t>
+          <t>7934; 19829</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40364; 62076</t>
+          <t>38290; 59022</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89272; 123846</t>
+          <t>71143; 99396</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23017; 40845</t>
+          <t>22979; 41082</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19866; 37306</t>
+          <t>20430; 37647</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83887; 113648</t>
+          <t>84504; 112894</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>164930; 210477</t>
+          <t>172607; 216364</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7244</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10584</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34758</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4361</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5043</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>15377</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25319</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7244</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10584</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58936</t>
+          <t>61671</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1489; 8380</t>
+          <t>3413; 11781</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2136; 9691</t>
+          <t>3970; 13140</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9581; 21933</t>
+          <t>6209; 16700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18837; 32649</t>
+          <t>25941; 44491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3508; 12117</t>
+          <t>1848; 9255</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3394; 13077</t>
+          <t>2082; 9406</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6318; 16269</t>
+          <t>10104; 22338</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25791; 43414</t>
+          <t>20218; 34754</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6931; 18093</t>
+          <t>6345; 16855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7518; 18830</t>
+          <t>7618; 19686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18669; 34180</t>
+          <t>18646; 34574</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47537; 70644</t>
+          <t>49798; 73125</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>165</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24141</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23211</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>71938</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>155447</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>25741</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20361</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>68778</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>116339</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24141</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23211</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71938</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>268849</t>
+          <t>279704</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18506; 34662</t>
+          <t>17335; 33220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13830; 27968</t>
+          <t>16688; 32387</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56846; 81368</t>
+          <t>58586; 84759</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100101; 131230</t>
+          <t>135027; 174902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17312; 32665</t>
+          <t>19209; 34955</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16690; 31697</t>
+          <t>14207; 28582</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60081; 86057</t>
+          <t>57202; 81714</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>131763; 173549</t>
+          <t>106109; 139724</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39819; 60805</t>
+          <t>39954; 63354</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34508; 53864</t>
+          <t>33764; 55641</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124700; 158533</t>
+          <t>122953; 158157</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>243120; 295973</t>
+          <t>254485; 306859</t>
         </is>
       </c>
     </row>
